--- a/artfynd/A 50033-2024 artfynd.xlsx
+++ b/artfynd/A 50033-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1547,6 +1547,122 @@
           <t>Trädportalen</t>
         </is>
       </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>125276211</v>
+      </c>
+      <c r="B9" t="n">
+        <v>108903</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sävserås V hagen, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>527488</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6348725</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stenberga</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>nyligen gallrad äldre hagmark</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Roger Karlsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Roger Karlsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50033-2024 artfynd.xlsx
+++ b/artfynd/A 50033-2024 artfynd.xlsx
@@ -1553,7 +1553,7 @@
         <v>125276211</v>
       </c>
       <c r="B9" t="n">
-        <v>108903</v>
+        <v>109082</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 50033-2024 artfynd.xlsx
+++ b/artfynd/A 50033-2024 artfynd.xlsx
@@ -1553,12 +1553,7 @@
         <v>125276211</v>
       </c>
       <c r="B9" t="n">
-        <v>109082</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109137</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 50033-2024 artfynd.xlsx
+++ b/artfynd/A 50033-2024 artfynd.xlsx
@@ -1553,7 +1553,7 @@
         <v>125276211</v>
       </c>
       <c r="B9" t="n">
-        <v>109137</v>
+        <v>109144</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 50033-2024 artfynd.xlsx
+++ b/artfynd/A 50033-2024 artfynd.xlsx
@@ -1553,7 +1553,7 @@
         <v>125276211</v>
       </c>
       <c r="B9" t="n">
-        <v>109144</v>
+        <v>109147</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 50033-2024 artfynd.xlsx
+++ b/artfynd/A 50033-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125276211</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -893,6 +903,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105136956</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105136957</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1113,6 +1133,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105136958</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1223,6 +1248,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105136959</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1333,6 +1363,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105136960</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1443,6 +1478,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105136966</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1553,8 +1593,23 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105136953</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>